--- a/test_doc/new_org/syllabus_5_mathematics.xlsx
+++ b/test_doc/new_org/syllabus_5_mathematics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,22 +465,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Addition and Subtraction</t>
+          <t>Decimals</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Column methods</t>
+          <t>Place value in decimals</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,26 +491,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Word problems</t>
+          <t>Operations on decimals</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiplication and Division</t>
+          <t>Fractions</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Multiplying big numbers</t>
+          <t>Types of fractions</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Long division</t>
+          <t>Operations on fractions</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,16 +531,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Factors and Multiples</t>
+          <t>Playing with Numbers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finding factors</t>
+          <t>Factors and multiples</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,190 +551,110 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Common multiples</t>
+          <t>Divisibility rules</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fractions</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equivalent fractions</t>
+          <t>HCF and LCM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Term 1</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Addition and Subtraction</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adding fractions</t>
+          <t>Column methods</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Decimals</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tenths and hundredths</t>
+          <t>Word problems</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="inlineStr">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Handling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pictographs and tally marks</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Term 2</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Money and measurement</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Shapes and Angles</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kinds of angles</t>
+          <t>Bar graphs</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="inlineStr">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Multiplication and Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Multiplying big numbers</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Term 2</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Measuring angles</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Area and Perimeter</t>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Perimeter of rectangles</t>
+          <t>Long division</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Area by counting squares</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Handling</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tally marks</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Reading bar charts</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Patterns and Symmetry</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Number patterns</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Lines of symmetry</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
         <v>3</v>
       </c>
     </row>
